--- a/sheets/대금율보/검수/양산도.xlsx
+++ b/sheets/대금율보/검수/양산도.xlsx
@@ -3175,8 +3175,7 @@
       <c r="G5" s="24"/>
       <c r="H5" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">㴌フ
-‹</t>
+          <t xml:space="preserve">㴌フ</t>
         </is>
       </c>
       <c r="I5" s="24"/>
@@ -3319,8 +3318,7 @@
       <c r="E8" s="24"/>
       <c r="F8" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">林
-‹</t>
+          <t xml:space="preserve">林</t>
         </is>
       </c>
       <c r="G8" s="24"/>
@@ -3462,8 +3460,7 @@
       <c r="C11" s="24"/>
       <c r="D11" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">㴌フ
-‹</t>
+          <t xml:space="preserve">㴌フ</t>
         </is>
       </c>
       <c r="E11" s="24"/>
@@ -3559,7 +3556,7 @@
       <c r="C13" s="23"/>
       <c r="D13" s="25" t="inlineStr">
         <is>
-          <t xml:space="preserve">林‹
+          <t xml:space="preserve">林
 –淋</t>
         </is>
       </c>
@@ -3627,11 +3624,7 @@
           <t xml:space="preserve">라</t>
         </is>
       </c>
-      <c r="H14" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="H14" s="21"/>
       <c r="I14" s="24"/>
       <c r="J14" s="21" t="inlineStr">
         <is>

--- a/sheets/대금율보/검수/양산도.xlsx
+++ b/sheets/대금율보/검수/양산도.xlsx
@@ -2991,24 +2991,24 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <cols>
     <col min="1" max="1" width="2" customWidth="1"/>
-    <col min="2" max="2" width="9" customWidth="1"/>
+    <col min="2" max="2" width="11.63" customWidth="1"/>
     <col min="3" max="3" width="6" customWidth="1"/>
-    <col min="4" max="4" width="9" customWidth="1"/>
+    <col min="4" max="4" width="11.63" customWidth="1"/>
     <col min="5" max="5" width="6" customWidth="1"/>
-    <col min="6" max="6" width="9" customWidth="1"/>
+    <col min="6" max="6" width="11.63" customWidth="1"/>
     <col min="7" max="7" width="6" customWidth="1"/>
-    <col min="8" max="8" width="9" customWidth="1"/>
+    <col min="8" max="8" width="11.63" customWidth="1"/>
     <col min="9" max="9" width="6" customWidth="1"/>
-    <col min="10" max="10" width="9" customWidth="1"/>
+    <col min="10" max="10" width="11.63" customWidth="1"/>
     <col min="11" max="11" width="6" customWidth="1"/>
-    <col min="12" max="12" width="9" customWidth="1"/>
+    <col min="12" max="12" width="11.63" customWidth="1"/>
     <col min="13" max="13" width="6" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" ht="6.0" customHeight="true">
       <c r="A1" s="0"/>
     </row>
-    <row r="2" ht="60" customHeight="1">
+    <row r="2" ht="50.63" customHeight="true">
       <c r="A2" s="0"/>
       <c r="B2" s="20" t="inlineStr">
         <is>
@@ -3027,7 +3027,7 @@
       <c r="L2" s="20"/>
       <c r="M2" s="20"/>
     </row>
-    <row r="3" ht="56" customHeight="1">
+    <row r="3" ht="75.27" customHeight="true">
       <c r="A3" s="0"/>
       <c r="B3" s="21" t="inlineStr">
         <is>
@@ -3086,7 +3086,7 @@
         </is>
       </c>
     </row>
-    <row r="4" ht="56" customHeight="1">
+    <row r="4" ht="75.27" customHeight="true">
       <c r="A4" s="0"/>
       <c r="B4" s="21" t="inlineStr">
         <is>
@@ -3147,7 +3147,7 @@
         </is>
       </c>
     </row>
-    <row r="5" ht="56" customHeight="1">
+    <row r="5" ht="75.27" customHeight="true">
       <c r="A5" s="0"/>
       <c r="B5" s="21" t="inlineStr">
         <is>
@@ -3192,7 +3192,7 @@
         </is>
       </c>
     </row>
-    <row r="6" ht="56" customHeight="1">
+    <row r="6" ht="75.27" customHeight="true">
       <c r="A6" s="0"/>
       <c r="B6" s="21" t="inlineStr">
         <is>
@@ -3255,7 +3255,7 @@
         </is>
       </c>
     </row>
-    <row r="7" ht="56" customHeight="1">
+    <row r="7" ht="75.27" customHeight="true">
       <c r="A7" s="0"/>
       <c r="B7" s="21" t="inlineStr">
         <is>
@@ -3306,7 +3306,7 @@
       <c r="L7" s="21"/>
       <c r="M7" s="23"/>
     </row>
-    <row r="8" ht="56" customHeight="1">
+    <row r="8" ht="75.27" customHeight="true">
       <c r="A8" s="0"/>
       <c r="B8" s="21"/>
       <c r="C8" s="24"/>
@@ -3342,7 +3342,7 @@
       <c r="L8" s="21"/>
       <c r="M8" s="24"/>
     </row>
-    <row r="9" ht="56" customHeight="1">
+    <row r="9" ht="75.27" customHeight="true">
       <c r="A9" s="0"/>
       <c r="B9" s="21" t="inlineStr">
         <is>
@@ -3398,7 +3398,7 @@
       <c r="L9" s="21"/>
       <c r="M9" s="22"/>
     </row>
-    <row r="10" ht="56" customHeight="1">
+    <row r="10" ht="75.27" customHeight="true">
       <c r="A10" s="0"/>
       <c r="B10" s="21" t="inlineStr">
         <is>
@@ -3449,7 +3449,7 @@
       <c r="L10" s="21"/>
       <c r="M10" s="23"/>
     </row>
-    <row r="11" ht="56" customHeight="1">
+    <row r="11" ht="75.27" customHeight="true">
       <c r="A11" s="0"/>
       <c r="B11" s="21" t="inlineStr">
         <is>
@@ -3490,7 +3490,7 @@
       <c r="L11" s="21"/>
       <c r="M11" s="24"/>
     </row>
-    <row r="12" ht="56" customHeight="1">
+    <row r="12" ht="75.27" customHeight="true">
       <c r="A12" s="0"/>
       <c r="B12" s="21" t="inlineStr">
         <is>
@@ -3545,7 +3545,7 @@
       <c r="L12" s="21"/>
       <c r="M12" s="22"/>
     </row>
-    <row r="13" ht="56" customHeight="1">
+    <row r="13" ht="75.27" customHeight="true">
       <c r="A13" s="0"/>
       <c r="B13" s="21" t="inlineStr">
         <is>
@@ -3595,7 +3595,7 @@
       <c r="L13" s="21"/>
       <c r="M13" s="23"/>
     </row>
-    <row r="14" ht="56" customHeight="1">
+    <row r="14" ht="75.27" customHeight="true">
       <c r="A14" s="0"/>
       <c r="B14" s="21" t="inlineStr">
         <is>
@@ -3645,6 +3645,6 @@
   </mergeCells>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.4" right="0.4" top="0.5" bottom="0.5" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" scale="100"/>
+  <pageSetup paperSize="9" orientation="portrait" scale="79"/>
 </worksheet>
 </file>